--- a/resources/templates/formato reportes.xlsx
+++ b/resources/templates/formato reportes.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fsanchez\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Towell\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C365B06-A386-4BD8-8AE2-B646DF8CFC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F748E7F-932C-4DB4-BDAC-398DEF54B49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{84822909-0E0F-4184-8C59-826A1580A2CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84822909-0E0F-4184-8C59-826A1580A2CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="129">
   <si>
     <t>Semana</t>
   </si>
@@ -259,6 +261,263 @@
   </si>
   <si>
     <t>S332</t>
+  </si>
+  <si>
+    <t>CLAVE</t>
+  </si>
+  <si>
+    <t>PENALIZACIÓN</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DEFECTO </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>URDIDO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ENGOMADO</t>
+    </r>
+  </si>
+  <si>
+    <t>5´S</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>RHC / PHC</t>
+  </si>
+  <si>
+    <t>HILOS CRUZADOS</t>
+  </si>
+  <si>
+    <t>RHS / PHS</t>
+  </si>
+  <si>
+    <t>HILOS SUELTOS</t>
+  </si>
+  <si>
+    <t>EPP</t>
+  </si>
+  <si>
+    <t>RHCE / PHCE</t>
+  </si>
+  <si>
+    <t>HILOS COLGANDO/ENTERRADOS</t>
+  </si>
+  <si>
+    <t>Basura</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>J CARLOS</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>PEDRO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>UBALDO</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>N/D/M/MA</t>
+  </si>
+  <si>
+    <t>NUDO MAL/DESPERDICIO HILO/MOTAS/MANCHADO</t>
+  </si>
+  <si>
+    <t>Rack/Ventilador</t>
+  </si>
+  <si>
+    <t>Amonestación</t>
+  </si>
+  <si>
+    <t>J / HP / HD</t>
+  </si>
+  <si>
+    <r>
+      <t>JULIO CON BORRA/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HILOS PEGADOS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/DÉBIL</t>
+    </r>
+  </si>
+  <si>
+    <t>Pasillo</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>MAL IDENTIFICADO</t>
+  </si>
+  <si>
+    <t>Máquina</t>
+  </si>
+  <si>
+    <t>Calidad</t>
+  </si>
+  <si>
+    <t>DM / TL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DIFERENCIA METRAJE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TELA LACIA</t>
+    </r>
+  </si>
+  <si>
+    <t>Olla/Canoa</t>
+  </si>
+  <si>
+    <t>FH / G</t>
+  </si>
+  <si>
+    <t>FALTANTE HILOS / GOLPEADA</t>
+  </si>
+  <si>
+    <t>Fuga Aceite</t>
+  </si>
+  <si>
+    <t>TF/Z/E</t>
+  </si>
+  <si>
+    <t>TELA FLOJA/ZANJAS/ENCIMADA</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>DIFERENTE TONO NO AUTORIZADO</t>
+  </si>
+  <si>
+    <t>Accidente</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>URD/ENG</t>
+  </si>
+  <si>
+    <t>JULIOS</t>
+  </si>
+  <si>
+    <t>DEFECTO</t>
+  </si>
+  <si>
+    <t>PENALIZAR</t>
+  </si>
+  <si>
+    <t>URD</t>
+  </si>
+  <si>
+    <t>RHS</t>
+  </si>
+  <si>
+    <t>RODRIGO</t>
+  </si>
+  <si>
+    <t>Penalizar</t>
+  </si>
+  <si>
+    <t>Seguridad 5`s</t>
   </si>
 </sst>
 </file>
@@ -269,7 +528,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +582,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,8 +653,56 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -560,11 +906,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF00B0F0"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00B0F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF00B0F0"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00B0F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -625,11 +1119,113 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,6 +1242,154 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectángulo 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CCF8661-7F95-4D51-BDD9-D176CED6169F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="2619375"/>
+          <a:ext cx="419100" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF3300"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="vert270" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>DEFECTOS DE CALIDAD</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectángulo 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E120FED-2A73-43FC-A3EF-A404734F96FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="7391400"/>
+          <a:ext cx="419100" cy="3838575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" vert="vert270" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1600" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>SEGURIDAD    Y    5`S</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -674,6 +1418,250 @@
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="URDIDO"/>
+      <sheetName val="ENGOMADO"/>
+      <sheetName val="URDIDO-ENGOMADO"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="4">
+          <cell r="AO4" t="str">
+            <v>DANIEL</v>
+          </cell>
+          <cell r="AP4" t="str">
+            <v>J CARLOS</v>
+          </cell>
+          <cell r="AQ4" t="str">
+            <v>ROBERTO</v>
+          </cell>
+          <cell r="AR4" t="str">
+            <v>MIGUEL</v>
+          </cell>
+          <cell r="AS4" t="str">
+            <v>PEDRO</v>
+          </cell>
+          <cell r="AT4" t="str">
+            <v>CARLOS G</v>
+          </cell>
+          <cell r="AX4" t="str">
+            <v>EDUARDO</v>
+          </cell>
+          <cell r="AY4" t="str">
+            <v>JESUS</v>
+          </cell>
+          <cell r="AZ4" t="str">
+            <v>UBALDO</v>
+          </cell>
+          <cell r="BA4" t="str">
+            <v>FRANCISCO</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AN5" t="str">
+            <v>Eficiencia</v>
+          </cell>
+          <cell r="AO5">
+            <v>80.833333333333343</v>
+          </cell>
+          <cell r="AP5">
+            <v>78.750000000000014</v>
+          </cell>
+          <cell r="AQ5">
+            <v>83.500000000000014</v>
+          </cell>
+          <cell r="AR5">
+            <v>76.999999999999986</v>
+          </cell>
+          <cell r="AS5">
+            <v>87.333333333333343</v>
+          </cell>
+          <cell r="AT5">
+            <v>78.166666666666657</v>
+          </cell>
+          <cell r="AW5" t="str">
+            <v>Eficiencia</v>
+          </cell>
+          <cell r="AX5">
+            <v>84.833333333333343</v>
+          </cell>
+          <cell r="AY5">
+            <v>77.833333333333329</v>
+          </cell>
+          <cell r="AZ5">
+            <v>85.833333333333329</v>
+          </cell>
+          <cell r="BA5">
+            <v>82.333333333333329</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="AN7" t="str">
+            <v>Calidad</v>
+          </cell>
+          <cell r="AO7">
+            <v>96.5</v>
+          </cell>
+          <cell r="AP7">
+            <v>100</v>
+          </cell>
+          <cell r="AQ7">
+            <v>97</v>
+          </cell>
+          <cell r="AR7">
+            <v>100</v>
+          </cell>
+          <cell r="AS7">
+            <v>100</v>
+          </cell>
+          <cell r="AT7">
+            <v>100</v>
+          </cell>
+          <cell r="AW7" t="str">
+            <v>Calidad</v>
+          </cell>
+          <cell r="AX7">
+            <v>94.5</v>
+          </cell>
+          <cell r="AY7">
+            <v>100</v>
+          </cell>
+          <cell r="AZ7">
+            <v>97</v>
+          </cell>
+          <cell r="BA7">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="AN8" t="str">
+            <v>5´S , Seguridad</v>
+          </cell>
+          <cell r="AO8">
+            <v>100</v>
+          </cell>
+          <cell r="AP8">
+            <v>100</v>
+          </cell>
+          <cell r="AQ8">
+            <v>100</v>
+          </cell>
+          <cell r="AR8">
+            <v>100</v>
+          </cell>
+          <cell r="AS8">
+            <v>100</v>
+          </cell>
+          <cell r="AT8">
+            <v>100</v>
+          </cell>
+          <cell r="AW8" t="str">
+            <v>5´S , Seguridad</v>
+          </cell>
+          <cell r="AX8">
+            <v>100</v>
+          </cell>
+          <cell r="AY8">
+            <v>100</v>
+          </cell>
+          <cell r="AZ8">
+            <v>100</v>
+          </cell>
+          <cell r="BA8">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="AN11" t="str">
+            <v>MERMA</v>
+          </cell>
+          <cell r="AO11">
+            <v>98.747601797809992</v>
+          </cell>
+          <cell r="AP11">
+            <v>100</v>
+          </cell>
+          <cell r="AQ11">
+            <v>98.803978164802558</v>
+          </cell>
+          <cell r="AR11">
+            <v>98.564599227792201</v>
+          </cell>
+          <cell r="AS11">
+            <v>99.298656552808126</v>
+          </cell>
+          <cell r="AT11">
+            <v>99.180777590931072</v>
+          </cell>
+          <cell r="AW11" t="str">
+            <v>MERMA</v>
+          </cell>
+          <cell r="AX11">
+            <v>98.171564537610678</v>
+          </cell>
+          <cell r="AY11">
+            <v>98.349090491987894</v>
+          </cell>
+          <cell r="AZ11">
+            <v>98.332646253643574</v>
+          </cell>
+          <cell r="BA11">
+            <v>98.416725254706492</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="AN12" t="str">
+            <v>OEE</v>
+          </cell>
+          <cell r="AO12">
+            <v>77.027243885700045</v>
+          </cell>
+          <cell r="AP12">
+            <v>78.750000000000028</v>
+          </cell>
+          <cell r="AQ12">
+            <v>80.026282114581846</v>
+          </cell>
+          <cell r="AR12">
+            <v>75.894741405399984</v>
+          </cell>
+          <cell r="AS12">
+            <v>86.720826722785773</v>
+          </cell>
+          <cell r="AT12">
+            <v>77.526307816911114</v>
+          </cell>
+          <cell r="AW12" t="str">
+            <v>OEE</v>
+          </cell>
+          <cell r="AX12">
+            <v>78.701689000689043</v>
+          </cell>
+          <cell r="AY12">
+            <v>76.54837543293057</v>
+          </cell>
+          <cell r="AZ12">
+            <v>81.870122393346065</v>
+          </cell>
+          <cell r="BA12">
+            <v>81.029770459708331</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -997,13 +1985,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66AE1D9-77A1-4CB3-B1C2-95FCDA87661D}">
   <dimension ref="A1:AB44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.77734375" customWidth="1"/>
-    <col min="3" max="3" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>3</v>
       </c>
@@ -1032,7 +2020,7 @@
       <c r="V1" s="5"/>
       <c r="W1" s="3"/>
     </row>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <f>D3+I3+N3</f>
         <v>3111.3</v>
@@ -1055,12 +2043,12 @@
       </c>
       <c r="V2" s="10"/>
     </row>
-    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="30">
+    <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="31">
         <v>46034</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="11">
         <f>SUM(D5:D44)</f>
         <v>539.40000000000009</v>
@@ -1095,7 +2083,7 @@
       </c>
       <c r="V3" s="5"/>
     </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="13" t="s">
         <v>6</v>
@@ -1159,7 +2147,7 @@
       </c>
       <c r="V4" s="5"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -1224,7 +2212,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1289,7 +2277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1344,7 +2332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1397,7 +2385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -1452,7 +2440,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -1507,7 +2495,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>7</v>
       </c>
@@ -1562,7 +2550,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -1615,7 +2603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>9</v>
       </c>
@@ -1650,7 +2638,7 @@
       <c r="T13" s="22"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -1685,7 +2673,7 @@
       <c r="T14" s="22"/>
       <c r="U14" s="23"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>11</v>
       </c>
@@ -1710,7 +2698,7 @@
       <c r="T15" s="22"/>
       <c r="U15" s="23"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -1735,7 +2723,7 @@
       <c r="T16" s="22"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>13</v>
       </c>
@@ -1760,7 +2748,7 @@
       <c r="T17" s="22"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -1785,7 +2773,7 @@
       <c r="T18" s="22"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>15</v>
       </c>
@@ -1810,7 +2798,7 @@
       <c r="T19" s="22"/>
       <c r="U19" s="23"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -1839,7 +2827,7 @@
       <c r="AA20" s="25"/>
       <c r="AB20" s="24"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>17</v>
       </c>
@@ -1868,7 +2856,7 @@
       <c r="AA21" s="25"/>
       <c r="AB21" s="24"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -1897,7 +2885,7 @@
       <c r="AA22" s="25"/>
       <c r="AB22" s="24"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>19</v>
       </c>
@@ -1926,7 +2914,7 @@
       <c r="AA23" s="25"/>
       <c r="AB23" s="24"/>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -1958,7 +2946,7 @@
       <c r="AA24" s="25"/>
       <c r="AB24" s="24"/>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>21</v>
       </c>
@@ -1987,7 +2975,7 @@
       <c r="AA25" s="25"/>
       <c r="AB25" s="24"/>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -2017,7 +3005,7 @@
       <c r="AA26" s="25"/>
       <c r="AB26" s="24"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>23</v>
       </c>
@@ -2047,7 +3035,7 @@
       <c r="AA27" s="25"/>
       <c r="AB27" s="24"/>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -2076,7 +3064,7 @@
       <c r="Z28" s="24"/>
       <c r="AA28" s="24"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>25</v>
       </c>
@@ -2105,7 +3093,7 @@
       <c r="Z29" s="24"/>
       <c r="AA29" s="24"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>26</v>
       </c>
@@ -2133,7 +3121,7 @@
       <c r="Z30" s="24"/>
       <c r="AA30" s="24"/>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>27</v>
       </c>
@@ -2161,7 +3149,7 @@
       <c r="Z31" s="24"/>
       <c r="AA31" s="24"/>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>28</v>
       </c>
@@ -2189,7 +3177,7 @@
       <c r="Z32" s="24"/>
       <c r="AA32" s="24"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>29</v>
       </c>
@@ -2218,7 +3206,7 @@
       <c r="Z33" s="24"/>
       <c r="AA33" s="24"/>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>30</v>
       </c>
@@ -2247,7 +3235,7 @@
       <c r="Z34" s="26"/>
       <c r="AA34" s="26"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>31</v>
       </c>
@@ -2275,7 +3263,7 @@
       <c r="Z35" s="24"/>
       <c r="AA35" s="24"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>32</v>
       </c>
@@ -2303,7 +3291,7 @@
       <c r="Z36" s="24"/>
       <c r="AA36" s="24"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>33</v>
       </c>
@@ -2331,7 +3319,7 @@
       <c r="Z37" s="24"/>
       <c r="AA37" s="24"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>34</v>
       </c>
@@ -2359,7 +3347,7 @@
       <c r="Z38" s="24"/>
       <c r="AA38" s="24"/>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>35</v>
       </c>
@@ -2387,7 +3375,7 @@
       <c r="Z39" s="24"/>
       <c r="AA39" s="24"/>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>36</v>
       </c>
@@ -2415,7 +3403,7 @@
       <c r="Z40" s="24"/>
       <c r="AA40" s="24"/>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>37</v>
       </c>
@@ -2443,7 +3431,7 @@
       <c r="Z41" s="24"/>
       <c r="AA41" s="24"/>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>38</v>
       </c>
@@ -2471,7 +3459,7 @@
       <c r="Z42" s="24"/>
       <c r="AA42" s="24"/>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>39</v>
       </c>
@@ -2499,7 +3487,7 @@
       <c r="Z43" s="24"/>
       <c r="AA43" s="24"/>
     </row>
-    <row r="44" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>40</v>
       </c>
@@ -2538,9 +3526,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6170556C-5B5C-448E-BE57-2F4EDF8C290C}">
   <dimension ref="A1:K308"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <f>[1]URDIDO!A1</f>
         <v>3</v>
@@ -2558,7 +3546,7 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <f>D3+I3</f>
         <v>3483.2999999999997</v>
@@ -2574,13 +3562,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="31">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="30">
         <f>[1]URDIDO!A3</f>
         <v>46034</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
       <c r="D3" s="11">
         <f>SUM(D5:D44)</f>
         <v>3124.7</v>
@@ -2598,7 +3586,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
       <c r="B4" s="13" t="s">
         <v>6</v>
@@ -2631,7 +3619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2666,7 +3654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2691,7 +3679,7 @@
       <c r="J6" s="22"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2716,7 +3704,7 @@
       <c r="J7" s="22"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2739,7 +3727,7 @@
       <c r="J8" s="22"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2754,7 +3742,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2769,7 +3757,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
         <v>7</v>
       </c>
@@ -2784,7 +3772,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -2799,7 +3787,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
         <v>9</v>
       </c>
@@ -2814,7 +3802,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2829,7 +3817,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="23"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
         <v>11</v>
       </c>
@@ -2844,7 +3832,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="23"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -2859,7 +3847,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>13</v>
       </c>
@@ -2874,7 +3862,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -2889,7 +3877,7 @@
       <c r="J18" s="22"/>
       <c r="K18" s="23"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>15</v>
       </c>
@@ -2904,7 +3892,7 @@
       <c r="J19" s="22"/>
       <c r="K19" s="23"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -2919,7 +3907,7 @@
       <c r="J20" s="22"/>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>17</v>
       </c>
@@ -2934,7 +3922,7 @@
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -2949,7 +3937,7 @@
       <c r="J22" s="22"/>
       <c r="K22" s="23"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>19</v>
       </c>
@@ -2964,7 +3952,7 @@
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -2979,7 +3967,7 @@
       <c r="J24" s="22"/>
       <c r="K24" s="23"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>21</v>
       </c>
@@ -2994,7 +3982,7 @@
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -3009,7 +3997,7 @@
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>23</v>
       </c>
@@ -3024,7 +4012,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -3039,7 +4027,7 @@
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>25</v>
       </c>
@@ -3054,7 +4042,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>26</v>
       </c>
@@ -3069,7 +4057,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="23"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>27</v>
       </c>
@@ -3084,7 +4072,7 @@
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>28</v>
       </c>
@@ -3099,7 +4087,7 @@
       <c r="J32" s="22"/>
       <c r="K32" s="23"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>29</v>
       </c>
@@ -3114,7 +4102,7 @@
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>30</v>
       </c>
@@ -3129,7 +4117,7 @@
       <c r="J34" s="22"/>
       <c r="K34" s="23"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>31</v>
       </c>
@@ -3144,7 +4132,7 @@
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>32</v>
       </c>
@@ -3159,7 +4147,7 @@
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>33</v>
       </c>
@@ -3174,7 +4162,7 @@
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>34</v>
       </c>
@@ -3189,7 +4177,7 @@
       <c r="J38" s="22"/>
       <c r="K38" s="23"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>35</v>
       </c>
@@ -3204,7 +4192,7 @@
       <c r="J39" s="22"/>
       <c r="K39" s="23"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>36</v>
       </c>
@@ -3219,7 +4207,7 @@
       <c r="J40" s="22"/>
       <c r="K40" s="23"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>37</v>
       </c>
@@ -3234,7 +4222,7 @@
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>38</v>
       </c>
@@ -3249,7 +4237,7 @@
       <c r="J42" s="22"/>
       <c r="K42" s="23"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>39</v>
       </c>
@@ -3264,7 +4252,7 @@
       <c r="J43" s="22"/>
       <c r="K43" s="23"/>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>40</v>
       </c>
@@ -3279,10 +4267,10 @@
       <c r="J44" s="28"/>
       <c r="K44" s="29"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
     </row>
-    <row r="46" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <f>D47+I47</f>
         <v>5877.9</v>
@@ -3298,13 +4286,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="31">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="30">
         <f>1+A3</f>
         <v>46035</v>
       </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
       <c r="D47" s="11">
         <f>SUM(D49:D88)</f>
         <v>5300.7999999999993</v>
@@ -3322,7 +4310,7 @@
         <v>1351.5</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48" s="13" t="s">
         <v>6</v>
@@ -3355,7 +4343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>1</v>
       </c>
@@ -3388,7 +4376,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>2</v>
       </c>
@@ -3423,7 +4411,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>3</v>
       </c>
@@ -3448,7 +4436,7 @@
       <c r="J51" s="22"/>
       <c r="K51" s="23"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <v>4</v>
       </c>
@@ -3471,7 +4459,7 @@
       <c r="J52" s="22"/>
       <c r="K52" s="23"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>5</v>
       </c>
@@ -3496,7 +4484,7 @@
       <c r="J53" s="22"/>
       <c r="K53" s="23"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <v>6</v>
       </c>
@@ -3521,7 +4509,7 @@
       <c r="J54" s="22"/>
       <c r="K54" s="23"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>7</v>
       </c>
@@ -3544,7 +4532,7 @@
       <c r="J55" s="22"/>
       <c r="K55" s="23"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="12">
         <v>8</v>
       </c>
@@ -3569,7 +4557,7 @@
       <c r="J56" s="22"/>
       <c r="K56" s="23"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="12">
         <v>9</v>
       </c>
@@ -3594,7 +4582,7 @@
       <c r="J57" s="22"/>
       <c r="K57" s="23"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="12">
         <v>10</v>
       </c>
@@ -3619,7 +4607,7 @@
       <c r="J58" s="22"/>
       <c r="K58" s="23"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="12">
         <v>11</v>
       </c>
@@ -3634,7 +4622,7 @@
       <c r="J59" s="22"/>
       <c r="K59" s="23"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="12">
         <v>12</v>
       </c>
@@ -3649,7 +4637,7 @@
       <c r="J60" s="22"/>
       <c r="K60" s="23"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="12">
         <v>13</v>
       </c>
@@ -3664,7 +4652,7 @@
       <c r="J61" s="22"/>
       <c r="K61" s="23"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="12">
         <v>14</v>
       </c>
@@ -3679,7 +4667,7 @@
       <c r="J62" s="22"/>
       <c r="K62" s="23"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="12">
         <v>15</v>
       </c>
@@ -3694,7 +4682,7 @@
       <c r="J63" s="22"/>
       <c r="K63" s="23"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="12">
         <v>16</v>
       </c>
@@ -3709,7 +4697,7 @@
       <c r="J64" s="22"/>
       <c r="K64" s="23"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="12">
         <v>17</v>
       </c>
@@ -3724,7 +4712,7 @@
       <c r="J65" s="22"/>
       <c r="K65" s="23"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="12">
         <v>18</v>
       </c>
@@ -3739,7 +4727,7 @@
       <c r="J66" s="22"/>
       <c r="K66" s="23"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="12">
         <v>19</v>
       </c>
@@ -3754,7 +4742,7 @@
       <c r="J67" s="22"/>
       <c r="K67" s="23"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="12">
         <v>20</v>
       </c>
@@ -3769,7 +4757,7 @@
       <c r="J68" s="22"/>
       <c r="K68" s="23"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="12">
         <v>21</v>
       </c>
@@ -3784,7 +4772,7 @@
       <c r="J69" s="22"/>
       <c r="K69" s="23"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="12">
         <v>22</v>
       </c>
@@ -3799,7 +4787,7 @@
       <c r="J70" s="22"/>
       <c r="K70" s="23"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="12">
         <v>23</v>
       </c>
@@ -3814,7 +4802,7 @@
       <c r="J71" s="22"/>
       <c r="K71" s="23"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="12">
         <v>24</v>
       </c>
@@ -3829,7 +4817,7 @@
       <c r="J72" s="22"/>
       <c r="K72" s="23"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="12">
         <v>25</v>
       </c>
@@ -3844,7 +4832,7 @@
       <c r="J73" s="22"/>
       <c r="K73" s="23"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="12">
         <v>26</v>
       </c>
@@ -3859,7 +4847,7 @@
       <c r="J74" s="22"/>
       <c r="K74" s="23"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="12">
         <v>27</v>
       </c>
@@ -3874,7 +4862,7 @@
       <c r="J75" s="22"/>
       <c r="K75" s="23"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="12">
         <v>28</v>
       </c>
@@ -3889,7 +4877,7 @@
       <c r="J76" s="22"/>
       <c r="K76" s="23"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="12">
         <v>29</v>
       </c>
@@ -3904,7 +4892,7 @@
       <c r="J77" s="22"/>
       <c r="K77" s="23"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="12">
         <v>30</v>
       </c>
@@ -3919,7 +4907,7 @@
       <c r="J78" s="22"/>
       <c r="K78" s="23"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="12">
         <v>31</v>
       </c>
@@ -3934,7 +4922,7 @@
       <c r="J79" s="22"/>
       <c r="K79" s="23"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="12">
         <v>32</v>
       </c>
@@ -3949,7 +4937,7 @@
       <c r="J80" s="22"/>
       <c r="K80" s="23"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="12">
         <v>33</v>
       </c>
@@ -3964,7 +4952,7 @@
       <c r="J81" s="22"/>
       <c r="K81" s="23"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="12">
         <v>34</v>
       </c>
@@ -3979,7 +4967,7 @@
       <c r="J82" s="22"/>
       <c r="K82" s="23"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="12">
         <v>35</v>
       </c>
@@ -3994,7 +4982,7 @@
       <c r="J83" s="22"/>
       <c r="K83" s="23"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="12">
         <v>36</v>
       </c>
@@ -4009,7 +4997,7 @@
       <c r="J84" s="22"/>
       <c r="K84" s="23"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="12">
         <v>37</v>
       </c>
@@ -4024,7 +5012,7 @@
       <c r="J85" s="22"/>
       <c r="K85" s="23"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="12">
         <v>38</v>
       </c>
@@ -4039,7 +5027,7 @@
       <c r="J86" s="22"/>
       <c r="K86" s="23"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="12">
         <v>39</v>
       </c>
@@ -4054,7 +5042,7 @@
       <c r="J87" s="22"/>
       <c r="K87" s="23"/>
     </row>
-    <row r="88" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12">
         <v>40</v>
       </c>
@@ -4069,10 +5057,10 @@
       <c r="J88" s="28"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
     </row>
-    <row r="90" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <f>D91+I91</f>
         <v>5360.5</v>
@@ -4088,13 +5076,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="31">
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="30">
         <f>1+A47</f>
         <v>46036</v>
       </c>
-      <c r="B91" s="31"/>
-      <c r="C91" s="31"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
       <c r="D91" s="11">
         <f>SUM(D93:D132)</f>
         <v>2903.4</v>
@@ -4112,7 +5100,7 @@
         <v>19600</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="12"/>
       <c r="B92" s="13" t="s">
         <v>6</v>
@@ -4145,7 +5133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="12">
         <v>1</v>
       </c>
@@ -4180,7 +5168,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="12">
         <v>2</v>
       </c>
@@ -4215,7 +5203,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="12">
         <v>3</v>
       </c>
@@ -4250,7 +5238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="12">
         <v>4</v>
       </c>
@@ -4285,7 +5273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="12">
         <v>5</v>
       </c>
@@ -4308,7 +5296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="12">
         <v>6</v>
       </c>
@@ -4323,7 +5311,7 @@
       <c r="J98" s="22"/>
       <c r="K98" s="23"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="12">
         <v>7</v>
       </c>
@@ -4338,7 +5326,7 @@
       <c r="J99" s="22"/>
       <c r="K99" s="23"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="12">
         <v>8</v>
       </c>
@@ -4353,7 +5341,7 @@
       <c r="J100" s="22"/>
       <c r="K100" s="23"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="12">
         <v>9</v>
       </c>
@@ -4368,7 +5356,7 @@
       <c r="J101" s="22"/>
       <c r="K101" s="23"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="12">
         <v>10</v>
       </c>
@@ -4383,7 +5371,7 @@
       <c r="J102" s="22"/>
       <c r="K102" s="23"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="12">
         <v>11</v>
       </c>
@@ -4398,7 +5386,7 @@
       <c r="J103" s="22"/>
       <c r="K103" s="23"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="12">
         <v>12</v>
       </c>
@@ -4413,7 +5401,7 @@
       <c r="J104" s="22"/>
       <c r="K104" s="23"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="12">
         <v>13</v>
       </c>
@@ -4428,7 +5416,7 @@
       <c r="J105" s="22"/>
       <c r="K105" s="23"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="12">
         <v>14</v>
       </c>
@@ -4443,7 +5431,7 @@
       <c r="J106" s="22"/>
       <c r="K106" s="23"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="12">
         <v>15</v>
       </c>
@@ -4458,7 +5446,7 @@
       <c r="J107" s="22"/>
       <c r="K107" s="23"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="12">
         <v>16</v>
       </c>
@@ -4473,7 +5461,7 @@
       <c r="J108" s="22"/>
       <c r="K108" s="23"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="12">
         <v>17</v>
       </c>
@@ -4488,7 +5476,7 @@
       <c r="J109" s="22"/>
       <c r="K109" s="23"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="12">
         <v>18</v>
       </c>
@@ -4503,7 +5491,7 @@
       <c r="J110" s="22"/>
       <c r="K110" s="23"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="12">
         <v>19</v>
       </c>
@@ -4518,7 +5506,7 @@
       <c r="J111" s="22"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="12">
         <v>20</v>
       </c>
@@ -4533,7 +5521,7 @@
       <c r="J112" s="22"/>
       <c r="K112" s="23"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="12">
         <v>21</v>
       </c>
@@ -4548,7 +5536,7 @@
       <c r="J113" s="22"/>
       <c r="K113" s="23"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="12">
         <v>22</v>
       </c>
@@ -4563,7 +5551,7 @@
       <c r="J114" s="22"/>
       <c r="K114" s="23"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="12">
         <v>23</v>
       </c>
@@ -4578,7 +5566,7 @@
       <c r="J115" s="22"/>
       <c r="K115" s="23"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="12">
         <v>24</v>
       </c>
@@ -4593,7 +5581,7 @@
       <c r="J116" s="22"/>
       <c r="K116" s="23"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="12">
         <v>25</v>
       </c>
@@ -4608,7 +5596,7 @@
       <c r="J117" s="22"/>
       <c r="K117" s="23"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="12">
         <v>26</v>
       </c>
@@ -4623,7 +5611,7 @@
       <c r="J118" s="22"/>
       <c r="K118" s="23"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="12">
         <v>27</v>
       </c>
@@ -4638,7 +5626,7 @@
       <c r="J119" s="22"/>
       <c r="K119" s="23"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="12">
         <v>28</v>
       </c>
@@ -4653,7 +5641,7 @@
       <c r="J120" s="22"/>
       <c r="K120" s="23"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="12">
         <v>29</v>
       </c>
@@ -4668,7 +5656,7 @@
       <c r="J121" s="22"/>
       <c r="K121" s="23"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="12">
         <v>30</v>
       </c>
@@ -4683,7 +5671,7 @@
       <c r="J122" s="22"/>
       <c r="K122" s="23"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="12">
         <v>31</v>
       </c>
@@ -4698,7 +5686,7 @@
       <c r="J123" s="22"/>
       <c r="K123" s="23"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="12">
         <v>32</v>
       </c>
@@ -4713,7 +5701,7 @@
       <c r="J124" s="22"/>
       <c r="K124" s="23"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="12">
         <v>33</v>
       </c>
@@ -4728,7 +5716,7 @@
       <c r="J125" s="22"/>
       <c r="K125" s="23"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="12">
         <v>34</v>
       </c>
@@ -4743,7 +5731,7 @@
       <c r="J126" s="22"/>
       <c r="K126" s="23"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="12">
         <v>35</v>
       </c>
@@ -4758,7 +5746,7 @@
       <c r="J127" s="22"/>
       <c r="K127" s="23"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="12">
         <v>36</v>
       </c>
@@ -4773,7 +5761,7 @@
       <c r="J128" s="22"/>
       <c r="K128" s="23"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="12">
         <v>37</v>
       </c>
@@ -4788,7 +5776,7 @@
       <c r="J129" s="22"/>
       <c r="K129" s="23"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="12">
         <v>38</v>
       </c>
@@ -4803,7 +5791,7 @@
       <c r="J130" s="22"/>
       <c r="K130" s="23"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="12">
         <v>39</v>
       </c>
@@ -4818,7 +5806,7 @@
       <c r="J131" s="22"/>
       <c r="K131" s="23"/>
     </row>
-    <row r="132" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12">
         <v>40</v>
       </c>
@@ -4833,10 +5821,10 @@
       <c r="J132" s="28"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="12"/>
     </row>
-    <row r="134" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
         <f>D135+I135</f>
         <v>8700.4</v>
@@ -4852,13 +5840,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="31">
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="30">
         <f>1+A91</f>
         <v>46037</v>
       </c>
-      <c r="B135" s="31"/>
-      <c r="C135" s="31"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
       <c r="D135" s="11">
         <f>SUM(D137:D176)</f>
         <v>4134.7</v>
@@ -4876,7 +5864,7 @@
         <v>31040</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12"/>
       <c r="B136" s="13" t="s">
         <v>6</v>
@@ -4909,7 +5897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>1</v>
       </c>
@@ -4944,7 +5932,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>2</v>
       </c>
@@ -4979,7 +5967,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>3</v>
       </c>
@@ -5012,7 +6000,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>4</v>
       </c>
@@ -5047,7 +6035,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>5</v>
       </c>
@@ -5080,7 +6068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>6</v>
       </c>
@@ -5105,7 +6093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>7</v>
       </c>
@@ -5130,7 +6118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>8</v>
       </c>
@@ -5145,7 +6133,7 @@
       <c r="J144" s="22"/>
       <c r="K144" s="23"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>9</v>
       </c>
@@ -5160,7 +6148,7 @@
       <c r="J145" s="22"/>
       <c r="K145" s="23"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>10</v>
       </c>
@@ -5175,7 +6163,7 @@
       <c r="J146" s="22"/>
       <c r="K146" s="23"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>11</v>
       </c>
@@ -5190,7 +6178,7 @@
       <c r="J147" s="22"/>
       <c r="K147" s="23"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>12</v>
       </c>
@@ -5205,7 +6193,7 @@
       <c r="J148" s="22"/>
       <c r="K148" s="23"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>13</v>
       </c>
@@ -5220,7 +6208,7 @@
       <c r="J149" s="22"/>
       <c r="K149" s="23"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>14</v>
       </c>
@@ -5235,7 +6223,7 @@
       <c r="J150" s="22"/>
       <c r="K150" s="23"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="12">
         <v>15</v>
       </c>
@@ -5250,7 +6238,7 @@
       <c r="J151" s="22"/>
       <c r="K151" s="23"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="12">
         <v>16</v>
       </c>
@@ -5265,7 +6253,7 @@
       <c r="J152" s="22"/>
       <c r="K152" s="23"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="12">
         <v>17</v>
       </c>
@@ -5280,7 +6268,7 @@
       <c r="J153" s="22"/>
       <c r="K153" s="23"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="12">
         <v>18</v>
       </c>
@@ -5295,7 +6283,7 @@
       <c r="J154" s="22"/>
       <c r="K154" s="23"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="12">
         <v>19</v>
       </c>
@@ -5310,7 +6298,7 @@
       <c r="J155" s="22"/>
       <c r="K155" s="23"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="12">
         <v>20</v>
       </c>
@@ -5325,7 +6313,7 @@
       <c r="J156" s="22"/>
       <c r="K156" s="23"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="12">
         <v>21</v>
       </c>
@@ -5340,7 +6328,7 @@
       <c r="J157" s="22"/>
       <c r="K157" s="23"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="12">
         <v>22</v>
       </c>
@@ -5355,7 +6343,7 @@
       <c r="J158" s="22"/>
       <c r="K158" s="23"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="12">
         <v>23</v>
       </c>
@@ -5370,7 +6358,7 @@
       <c r="J159" s="22"/>
       <c r="K159" s="23"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="12">
         <v>24</v>
       </c>
@@ -5385,7 +6373,7 @@
       <c r="J160" s="22"/>
       <c r="K160" s="23"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="12">
         <v>25</v>
       </c>
@@ -5400,7 +6388,7 @@
       <c r="J161" s="22"/>
       <c r="K161" s="23"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="12">
         <v>26</v>
       </c>
@@ -5415,7 +6403,7 @@
       <c r="J162" s="22"/>
       <c r="K162" s="23"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="12">
         <v>27</v>
       </c>
@@ -5430,7 +6418,7 @@
       <c r="J163" s="22"/>
       <c r="K163" s="23"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="12">
         <v>28</v>
       </c>
@@ -5445,7 +6433,7 @@
       <c r="J164" s="22"/>
       <c r="K164" s="23"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="12">
         <v>29</v>
       </c>
@@ -5460,7 +6448,7 @@
       <c r="J165" s="22"/>
       <c r="K165" s="23"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="12">
         <v>30</v>
       </c>
@@ -5475,7 +6463,7 @@
       <c r="J166" s="22"/>
       <c r="K166" s="23"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="12">
         <v>31</v>
       </c>
@@ -5490,7 +6478,7 @@
       <c r="J167" s="22"/>
       <c r="K167" s="23"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="12">
         <v>32</v>
       </c>
@@ -5505,7 +6493,7 @@
       <c r="J168" s="22"/>
       <c r="K168" s="23"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="12">
         <v>33</v>
       </c>
@@ -5520,7 +6508,7 @@
       <c r="J169" s="22"/>
       <c r="K169" s="23"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="12">
         <v>34</v>
       </c>
@@ -5535,7 +6523,7 @@
       <c r="J170" s="22"/>
       <c r="K170" s="23"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="12">
         <v>35</v>
       </c>
@@ -5550,7 +6538,7 @@
       <c r="J171" s="22"/>
       <c r="K171" s="23"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="12">
         <v>36</v>
       </c>
@@ -5565,7 +6553,7 @@
       <c r="J172" s="22"/>
       <c r="K172" s="23"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="12">
         <v>37</v>
       </c>
@@ -5580,7 +6568,7 @@
       <c r="J173" s="22"/>
       <c r="K173" s="23"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="12">
         <v>38</v>
       </c>
@@ -5595,7 +6583,7 @@
       <c r="J174" s="22"/>
       <c r="K174" s="23"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="12">
         <v>39</v>
       </c>
@@ -5610,7 +6598,7 @@
       <c r="J175" s="22"/>
       <c r="K175" s="23"/>
     </row>
-    <row r="176" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12">
         <v>40</v>
       </c>
@@ -5625,10 +6613,10 @@
       <c r="J176" s="28"/>
       <c r="K176" s="29"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="12"/>
     </row>
-    <row r="178" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
         <f>D179+I179</f>
         <v>6369.4</v>
@@ -5644,13 +6632,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="31">
+    <row r="179" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="30">
         <f>1+A135</f>
         <v>46038</v>
       </c>
-      <c r="B179" s="31"/>
-      <c r="C179" s="31"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
       <c r="D179" s="11">
         <f>SUM(D181:D220)</f>
         <v>2931.7</v>
@@ -5668,7 +6656,7 @@
         <v>21350</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="13" t="s">
         <v>6</v>
@@ -5701,7 +6689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="12">
         <v>1</v>
       </c>
@@ -5736,7 +6724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="12">
         <v>2</v>
       </c>
@@ -5769,7 +6757,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="12">
         <v>3</v>
       </c>
@@ -5804,7 +6792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="12">
         <v>4</v>
       </c>
@@ -5827,7 +6815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="12">
         <v>5</v>
       </c>
@@ -5852,7 +6840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="12">
         <v>6</v>
       </c>
@@ -5877,7 +6865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="12">
         <v>7</v>
       </c>
@@ -5892,7 +6880,7 @@
       <c r="J187" s="22"/>
       <c r="K187" s="20"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="12">
         <v>8</v>
       </c>
@@ -5907,7 +6895,7 @@
       <c r="J188" s="22"/>
       <c r="K188" s="20"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="12">
         <v>9</v>
       </c>
@@ -5922,7 +6910,7 @@
       <c r="J189" s="22"/>
       <c r="K189" s="23"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="12">
         <v>10</v>
       </c>
@@ -5937,7 +6925,7 @@
       <c r="J190" s="22"/>
       <c r="K190" s="23"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>11</v>
       </c>
@@ -5952,7 +6940,7 @@
       <c r="J191" s="22"/>
       <c r="K191" s="23"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>12</v>
       </c>
@@ -5967,7 +6955,7 @@
       <c r="J192" s="22"/>
       <c r="K192" s="23"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>13</v>
       </c>
@@ -5982,7 +6970,7 @@
       <c r="J193" s="22"/>
       <c r="K193" s="23"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>14</v>
       </c>
@@ -5997,7 +6985,7 @@
       <c r="J194" s="22"/>
       <c r="K194" s="23"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>15</v>
       </c>
@@ -6012,7 +7000,7 @@
       <c r="J195" s="22"/>
       <c r="K195" s="23"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>16</v>
       </c>
@@ -6027,7 +7015,7 @@
       <c r="J196" s="22"/>
       <c r="K196" s="23"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>17</v>
       </c>
@@ -6042,7 +7030,7 @@
       <c r="J197" s="22"/>
       <c r="K197" s="23"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>18</v>
       </c>
@@ -6057,7 +7045,7 @@
       <c r="J198" s="22"/>
       <c r="K198" s="23"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>19</v>
       </c>
@@ -6072,7 +7060,7 @@
       <c r="J199" s="22"/>
       <c r="K199" s="23"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <v>20</v>
       </c>
@@ -6087,7 +7075,7 @@
       <c r="J200" s="22"/>
       <c r="K200" s="23"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>21</v>
       </c>
@@ -6102,7 +7090,7 @@
       <c r="J201" s="22"/>
       <c r="K201" s="23"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="12">
         <v>22</v>
       </c>
@@ -6117,7 +7105,7 @@
       <c r="J202" s="22"/>
       <c r="K202" s="23"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="12">
         <v>23</v>
       </c>
@@ -6132,7 +7120,7 @@
       <c r="J203" s="22"/>
       <c r="K203" s="23"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>24</v>
       </c>
@@ -6147,7 +7135,7 @@
       <c r="J204" s="22"/>
       <c r="K204" s="23"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>25</v>
       </c>
@@ -6162,7 +7150,7 @@
       <c r="J205" s="22"/>
       <c r="K205" s="23"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="12">
         <v>26</v>
       </c>
@@ -6177,7 +7165,7 @@
       <c r="J206" s="22"/>
       <c r="K206" s="23"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="12">
         <v>27</v>
       </c>
@@ -6192,7 +7180,7 @@
       <c r="J207" s="22"/>
       <c r="K207" s="23"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="12">
         <v>28</v>
       </c>
@@ -6207,7 +7195,7 @@
       <c r="J208" s="22"/>
       <c r="K208" s="23"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>29</v>
       </c>
@@ -6222,7 +7210,7 @@
       <c r="J209" s="22"/>
       <c r="K209" s="23"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>30</v>
       </c>
@@ -6237,7 +7225,7 @@
       <c r="J210" s="22"/>
       <c r="K210" s="23"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>31</v>
       </c>
@@ -6252,7 +7240,7 @@
       <c r="J211" s="22"/>
       <c r="K211" s="23"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>32</v>
       </c>
@@ -6267,7 +7255,7 @@
       <c r="J212" s="22"/>
       <c r="K212" s="23"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>33</v>
       </c>
@@ -6282,7 +7270,7 @@
       <c r="J213" s="22"/>
       <c r="K213" s="23"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>34</v>
       </c>
@@ -6297,7 +7285,7 @@
       <c r="J214" s="22"/>
       <c r="K214" s="23"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>35</v>
       </c>
@@ -6312,7 +7300,7 @@
       <c r="J215" s="22"/>
       <c r="K215" s="23"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="12">
         <v>36</v>
       </c>
@@ -6327,7 +7315,7 @@
       <c r="J216" s="22"/>
       <c r="K216" s="23"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="12">
         <v>37</v>
       </c>
@@ -6342,7 +7330,7 @@
       <c r="J217" s="22"/>
       <c r="K217" s="23"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="12">
         <v>38</v>
       </c>
@@ -6357,7 +7345,7 @@
       <c r="J218" s="22"/>
       <c r="K218" s="23"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="12">
         <v>39</v>
       </c>
@@ -6372,7 +7360,7 @@
       <c r="J219" s="22"/>
       <c r="K219" s="23"/>
     </row>
-    <row r="220" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12">
         <v>40</v>
       </c>
@@ -6387,10 +7375,10 @@
       <c r="J220" s="28"/>
       <c r="K220" s="29"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="12"/>
     </row>
-    <row r="222" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
         <f>D223+I223</f>
         <v>6847.9000000000005</v>
@@ -6406,13 +7394,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="31">
+    <row r="223" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="30">
         <f>1+A179</f>
         <v>46039</v>
       </c>
-      <c r="B223" s="31"/>
-      <c r="C223" s="31"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="30"/>
       <c r="D223" s="11">
         <f>SUM(D225:D264)</f>
         <v>3741.6000000000004</v>
@@ -6430,7 +7418,7 @@
         <v>19250</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12"/>
       <c r="B224" s="13" t="s">
         <v>6</v>
@@ -6463,7 +7451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="12">
         <v>1</v>
       </c>
@@ -6498,7 +7486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="12">
         <v>2</v>
       </c>
@@ -6533,7 +7521,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="12">
         <v>3</v>
       </c>
@@ -6568,7 +7556,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="12">
         <v>4</v>
       </c>
@@ -6601,7 +7589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="12">
         <v>5</v>
       </c>
@@ -6636,7 +7624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="12">
         <v>6</v>
       </c>
@@ -6659,7 +7647,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="12">
         <v>7</v>
       </c>
@@ -6674,7 +7662,7 @@
       <c r="J231" s="22"/>
       <c r="K231" s="23"/>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="12">
         <v>8</v>
       </c>
@@ -6689,7 +7677,7 @@
       <c r="J232" s="22"/>
       <c r="K232" s="23"/>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="12">
         <v>9</v>
       </c>
@@ -6704,7 +7692,7 @@
       <c r="J233" s="22"/>
       <c r="K233" s="23"/>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="12">
         <v>10</v>
       </c>
@@ -6719,7 +7707,7 @@
       <c r="J234" s="22"/>
       <c r="K234" s="23"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="12">
         <v>11</v>
       </c>
@@ -6734,7 +7722,7 @@
       <c r="J235" s="22"/>
       <c r="K235" s="23"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="12">
         <v>12</v>
       </c>
@@ -6749,7 +7737,7 @@
       <c r="J236" s="22"/>
       <c r="K236" s="23"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="12">
         <v>13</v>
       </c>
@@ -6764,7 +7752,7 @@
       <c r="J237" s="22"/>
       <c r="K237" s="23"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="12">
         <v>14</v>
       </c>
@@ -6779,7 +7767,7 @@
       <c r="J238" s="22"/>
       <c r="K238" s="23"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="12">
         <v>15</v>
       </c>
@@ -6794,7 +7782,7 @@
       <c r="J239" s="22"/>
       <c r="K239" s="23"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="12">
         <v>16</v>
       </c>
@@ -6809,7 +7797,7 @@
       <c r="J240" s="22"/>
       <c r="K240" s="23"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="12">
         <v>17</v>
       </c>
@@ -6824,7 +7812,7 @@
       <c r="J241" s="22"/>
       <c r="K241" s="23"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="12">
         <v>18</v>
       </c>
@@ -6839,7 +7827,7 @@
       <c r="J242" s="22"/>
       <c r="K242" s="23"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="12">
         <v>19</v>
       </c>
@@ -6854,7 +7842,7 @@
       <c r="J243" s="22"/>
       <c r="K243" s="23"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="12">
         <v>20</v>
       </c>
@@ -6869,7 +7857,7 @@
       <c r="J244" s="22"/>
       <c r="K244" s="23"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="12">
         <v>21</v>
       </c>
@@ -6884,7 +7872,7 @@
       <c r="J245" s="22"/>
       <c r="K245" s="23"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="12">
         <v>22</v>
       </c>
@@ -6899,7 +7887,7 @@
       <c r="J246" s="22"/>
       <c r="K246" s="23"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="12">
         <v>23</v>
       </c>
@@ -6914,7 +7902,7 @@
       <c r="J247" s="22"/>
       <c r="K247" s="23"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="12">
         <v>24</v>
       </c>
@@ -6929,7 +7917,7 @@
       <c r="J248" s="22"/>
       <c r="K248" s="23"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="12">
         <v>25</v>
       </c>
@@ -6944,7 +7932,7 @@
       <c r="J249" s="22"/>
       <c r="K249" s="23"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="12">
         <v>26</v>
       </c>
@@ -6959,7 +7947,7 @@
       <c r="J250" s="22"/>
       <c r="K250" s="23"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="12">
         <v>27</v>
       </c>
@@ -6974,7 +7962,7 @@
       <c r="J251" s="22"/>
       <c r="K251" s="23"/>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="12">
         <v>28</v>
       </c>
@@ -6989,7 +7977,7 @@
       <c r="J252" s="22"/>
       <c r="K252" s="23"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="12">
         <v>29</v>
       </c>
@@ -7004,7 +7992,7 @@
       <c r="J253" s="22"/>
       <c r="K253" s="23"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="12">
         <v>30</v>
       </c>
@@ -7019,7 +8007,7 @@
       <c r="J254" s="22"/>
       <c r="K254" s="23"/>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="12">
         <v>31</v>
       </c>
@@ -7034,7 +8022,7 @@
       <c r="J255" s="22"/>
       <c r="K255" s="23"/>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="12">
         <v>32</v>
       </c>
@@ -7049,7 +8037,7 @@
       <c r="J256" s="22"/>
       <c r="K256" s="23"/>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="12">
         <v>33</v>
       </c>
@@ -7064,7 +8052,7 @@
       <c r="J257" s="22"/>
       <c r="K257" s="23"/>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="12">
         <v>34</v>
       </c>
@@ -7079,7 +8067,7 @@
       <c r="J258" s="22"/>
       <c r="K258" s="23"/>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="12">
         <v>35</v>
       </c>
@@ -7094,7 +8082,7 @@
       <c r="J259" s="22"/>
       <c r="K259" s="23"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="12">
         <v>36</v>
       </c>
@@ -7109,7 +8097,7 @@
       <c r="J260" s="22"/>
       <c r="K260" s="23"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="12">
         <v>37</v>
       </c>
@@ -7124,7 +8112,7 @@
       <c r="J261" s="22"/>
       <c r="K261" s="23"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="12">
         <v>38</v>
       </c>
@@ -7139,7 +8127,7 @@
       <c r="J262" s="22"/>
       <c r="K262" s="23"/>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="12">
         <v>39</v>
       </c>
@@ -7154,7 +8142,7 @@
       <c r="J263" s="22"/>
       <c r="K263" s="23"/>
     </row>
-    <row r="264" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12">
         <v>40</v>
       </c>
@@ -7169,10 +8157,10 @@
       <c r="J264" s="28"/>
       <c r="K264" s="29"/>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="12"/>
     </row>
-    <row r="266" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
         <f>D267+I267</f>
         <v>5109.8</v>
@@ -7188,13 +8176,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="31">
+    <row r="267" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="30">
         <f>1+A223</f>
         <v>46040</v>
       </c>
-      <c r="B267" s="31"/>
-      <c r="C267" s="31"/>
+      <c r="B267" s="30"/>
+      <c r="C267" s="30"/>
       <c r="D267" s="11">
         <f>SUM(D269:D308)</f>
         <v>1261.2</v>
@@ -7212,7 +8200,7 @@
         <v>23180</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12"/>
       <c r="B268" s="13" t="s">
         <v>6</v>
@@ -7245,7 +8233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="12">
         <v>1</v>
       </c>
@@ -7280,7 +8268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="12">
         <v>2</v>
       </c>
@@ -7315,7 +8303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="12">
         <v>3</v>
       </c>
@@ -7340,7 +8328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="12">
         <v>4</v>
       </c>
@@ -7365,7 +8353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="12">
         <v>5</v>
       </c>
@@ -7390,7 +8378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="12">
         <v>6</v>
       </c>
@@ -7413,7 +8401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="12">
         <v>7</v>
       </c>
@@ -7428,7 +8416,7 @@
       <c r="J275" s="22"/>
       <c r="K275" s="23"/>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="12">
         <v>8</v>
       </c>
@@ -7443,7 +8431,7 @@
       <c r="J276" s="22"/>
       <c r="K276" s="23"/>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="12">
         <v>9</v>
       </c>
@@ -7458,7 +8446,7 @@
       <c r="J277" s="22"/>
       <c r="K277" s="23"/>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="12">
         <v>10</v>
       </c>
@@ -7473,7 +8461,7 @@
       <c r="J278" s="22"/>
       <c r="K278" s="23"/>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="12">
         <v>11</v>
       </c>
@@ -7488,7 +8476,7 @@
       <c r="J279" s="22"/>
       <c r="K279" s="23"/>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="12">
         <v>12</v>
       </c>
@@ -7503,7 +8491,7 @@
       <c r="J280" s="22"/>
       <c r="K280" s="23"/>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="12">
         <v>13</v>
       </c>
@@ -7518,7 +8506,7 @@
       <c r="J281" s="22"/>
       <c r="K281" s="23"/>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="12">
         <v>14</v>
       </c>
@@ -7533,7 +8521,7 @@
       <c r="J282" s="22"/>
       <c r="K282" s="23"/>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="12">
         <v>15</v>
       </c>
@@ -7548,7 +8536,7 @@
       <c r="J283" s="22"/>
       <c r="K283" s="23"/>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="12">
         <v>16</v>
       </c>
@@ -7563,7 +8551,7 @@
       <c r="J284" s="22"/>
       <c r="K284" s="23"/>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="12">
         <v>17</v>
       </c>
@@ -7578,7 +8566,7 @@
       <c r="J285" s="22"/>
       <c r="K285" s="23"/>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="12">
         <v>18</v>
       </c>
@@ -7593,7 +8581,7 @@
       <c r="J286" s="22"/>
       <c r="K286" s="23"/>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="12">
         <v>19</v>
       </c>
@@ -7608,7 +8596,7 @@
       <c r="J287" s="22"/>
       <c r="K287" s="23"/>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="12">
         <v>20</v>
       </c>
@@ -7623,7 +8611,7 @@
       <c r="J288" s="22"/>
       <c r="K288" s="23"/>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="12">
         <v>21</v>
       </c>
@@ -7638,7 +8626,7 @@
       <c r="J289" s="22"/>
       <c r="K289" s="23"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="12">
         <v>22</v>
       </c>
@@ -7653,7 +8641,7 @@
       <c r="J290" s="22"/>
       <c r="K290" s="23"/>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="12">
         <v>23</v>
       </c>
@@ -7668,7 +8656,7 @@
       <c r="J291" s="22"/>
       <c r="K291" s="23"/>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="12">
         <v>24</v>
       </c>
@@ -7683,7 +8671,7 @@
       <c r="J292" s="22"/>
       <c r="K292" s="23"/>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="12">
         <v>25</v>
       </c>
@@ -7698,7 +8686,7 @@
       <c r="J293" s="22"/>
       <c r="K293" s="23"/>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="12">
         <v>26</v>
       </c>
@@ -7713,7 +8701,7 @@
       <c r="J294" s="22"/>
       <c r="K294" s="23"/>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="12">
         <v>27</v>
       </c>
@@ -7728,7 +8716,7 @@
       <c r="J295" s="22"/>
       <c r="K295" s="23"/>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="12">
         <v>28</v>
       </c>
@@ -7743,7 +8731,7 @@
       <c r="J296" s="22"/>
       <c r="K296" s="23"/>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="12">
         <v>29</v>
       </c>
@@ -7758,7 +8746,7 @@
       <c r="J297" s="22"/>
       <c r="K297" s="23"/>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="12">
         <v>30</v>
       </c>
@@ -7773,7 +8761,7 @@
       <c r="J298" s="22"/>
       <c r="K298" s="23"/>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="12">
         <v>31</v>
       </c>
@@ -7788,7 +8776,7 @@
       <c r="J299" s="22"/>
       <c r="K299" s="23"/>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="12">
         <v>32</v>
       </c>
@@ -7803,7 +8791,7 @@
       <c r="J300" s="22"/>
       <c r="K300" s="23"/>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="12">
         <v>33</v>
       </c>
@@ -7818,7 +8806,7 @@
       <c r="J301" s="22"/>
       <c r="K301" s="23"/>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="12">
         <v>34</v>
       </c>
@@ -7833,7 +8821,7 @@
       <c r="J302" s="22"/>
       <c r="K302" s="23"/>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="12">
         <v>35</v>
       </c>
@@ -7848,7 +8836,7 @@
       <c r="J303" s="22"/>
       <c r="K303" s="23"/>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="12">
         <v>36</v>
       </c>
@@ -7863,7 +8851,7 @@
       <c r="J304" s="22"/>
       <c r="K304" s="23"/>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="12">
         <v>37</v>
       </c>
@@ -7878,7 +8866,7 @@
       <c r="J305" s="22"/>
       <c r="K305" s="23"/>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="12">
         <v>38</v>
       </c>
@@ -7893,7 +8881,7 @@
       <c r="J306" s="22"/>
       <c r="K306" s="23"/>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="12">
         <v>39</v>
       </c>
@@ -7908,7 +8896,7 @@
       <c r="J307" s="22"/>
       <c r="K307" s="23"/>
     </row>
-    <row r="308" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="12">
         <v>40</v>
       </c>
@@ -7935,4 +8923,1273 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A067DD42-1052-4F56-99E2-123D56A0D5A1}">
+  <dimension ref="A1:I76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="31.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="35">
+        <v>1</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="35">
+        <v>2</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="37"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="B5" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="39">
+        <v>5</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="39">
+        <v>10</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="46">
+        <v>25</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="45">
+        <v>25</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="37"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="47">
+        <v>30</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="47">
+        <v>35</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="49">
+        <v>40</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" s="51">
+        <v>45992</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="37">
+        <v>3860</v>
+      </c>
+      <c r="E14" s="37">
+        <v>72</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="5"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" s="51"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>9</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23" s="51"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>11</v>
+      </c>
+      <c r="B24" s="51"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25" s="51"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>13</v>
+      </c>
+      <c r="B26" s="51"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>14</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>15</v>
+      </c>
+      <c r="B28" s="51"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>16</v>
+      </c>
+      <c r="B29" s="51"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>17</v>
+      </c>
+      <c r="B30" s="51"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>18</v>
+      </c>
+      <c r="B31" s="51"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>19</v>
+      </c>
+      <c r="B32" s="51"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>20</v>
+      </c>
+      <c r="B33" s="51"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>21</v>
+      </c>
+      <c r="B34" s="51"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>22</v>
+      </c>
+      <c r="B35" s="51"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>23</v>
+      </c>
+      <c r="B36" s="51"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>24</v>
+      </c>
+      <c r="B37" s="51"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>25</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1</v>
+      </c>
+      <c r="B39" s="54"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" s="57"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41" s="57"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" s="57"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>5</v>
+      </c>
+      <c r="B43" s="57"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>6</v>
+      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45" s="57"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>8</v>
+      </c>
+      <c r="B46" s="57"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>9</v>
+      </c>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>10</v>
+      </c>
+      <c r="B48" s="57"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49" s="57"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>12</v>
+      </c>
+      <c r="B50" s="57"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>13</v>
+      </c>
+      <c r="B51" s="57"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>14</v>
+      </c>
+      <c r="B52" s="57"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="5"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>15</v>
+      </c>
+      <c r="B53" s="57"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>16</v>
+      </c>
+      <c r="B54" s="57"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>17</v>
+      </c>
+      <c r="B55" s="57"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>18</v>
+      </c>
+      <c r="B56" s="57"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>19</v>
+      </c>
+      <c r="B57" s="57"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>20</v>
+      </c>
+      <c r="B58" s="60"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="62"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F60" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" s="24"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" s="37">
+        <f>SUMIF(G14:G38,"DP",H14:H38)</f>
+        <v>1.5</v>
+      </c>
+      <c r="C61" s="37">
+        <f>SUMIF(G14:G38,"JC",H14:H38)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="37">
+        <f>SUMIF($G14:$G38,"RB",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="37">
+        <f>SUMIF($G14:$G38,"MS",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="37">
+        <f>SUMIF($G14:$G38,"PC",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="G61" s="37">
+        <f>SUMIF($G14:$G38,"RC",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="24"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="50">
+        <f t="shared" ref="B62:G62" si="0">100-B61</f>
+        <v>98.5</v>
+      </c>
+      <c r="C62" s="50">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D62" s="50">
+        <f>100-D61</f>
+        <v>100</v>
+      </c>
+      <c r="E62" s="50">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="F62" s="50">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="G62" s="50">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H62" s="24"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="9"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="9"/>
+      <c r="B64" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="H64" s="24"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="37">
+        <f>SUMIF($G14:$G38,"EL",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="37">
+        <f>SUMIF($G14:$G38,"JR",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="37">
+        <f>SUMIF($G14:$G38,"UE",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="E65" s="37">
+        <f>SUMIF($G14:$G38,"FC",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="37">
+        <f>SUMIF($G14:$G38,"CM",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="37">
+        <f>SUMIF($G14:$G38,"RJ",$H14:$H38)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="24"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="50">
+        <f>100-B65</f>
+        <v>100</v>
+      </c>
+      <c r="C66" s="50">
+        <f t="shared" ref="C66:G66" si="1">100-C65</f>
+        <v>100</v>
+      </c>
+      <c r="D66" s="50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="E66" s="50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="F66" s="50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="G66" s="50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="H66" s="24"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="64" t="str">
+        <f t="shared" ref="B68:G68" si="2">B60</f>
+        <v>DANIEL</v>
+      </c>
+      <c r="C68" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v>J CARLOS</v>
+      </c>
+      <c r="D68" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v>ROBERTO</v>
+      </c>
+      <c r="E68" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v>MIGUEL</v>
+      </c>
+      <c r="F68" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v>PEDRO</v>
+      </c>
+      <c r="G68" s="64" t="str">
+        <f t="shared" si="2"/>
+        <v>RODRIGO</v>
+      </c>
+      <c r="H68" s="24"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="37">
+        <f>SUMIF(G39:G58,"DP",H39:H58)</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="37">
+        <f>SUMIF(G39:G58,"JC",H39:H58)</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="37">
+        <f>SUMIF($G39:$G58,"RB",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="E69" s="37">
+        <f>SUMIF($G39:$G58,"MS",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="37">
+        <f>SUMIF($G39:$G58,"PC",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="G69" s="37">
+        <f>SUMIF($G39:$G58,"RC",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="24"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="50">
+        <f t="shared" ref="B70:G70" si="3">100-B69</f>
+        <v>100</v>
+      </c>
+      <c r="C70" s="50">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="D70" s="50">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="E70" s="50">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="F70" s="50">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="G70" s="50">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H70" s="24"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="9"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="9"/>
+      <c r="B72" s="64" t="str">
+        <f t="shared" ref="B72:G72" si="4">B64</f>
+        <v>EDUARDO</v>
+      </c>
+      <c r="C72" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>JESUS</v>
+      </c>
+      <c r="D72" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>UBALDO</v>
+      </c>
+      <c r="E72" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>FRANCISCO</v>
+      </c>
+      <c r="F72" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>CARLOS</v>
+      </c>
+      <c r="G72" s="64" t="str">
+        <f t="shared" si="4"/>
+        <v>RAFAEL</v>
+      </c>
+      <c r="H72" s="24"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" s="37">
+        <f>SUMIF($G39:$G58,"EL",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="37">
+        <f>SUMIF($G39:$G58,"JR",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="37">
+        <f>SUMIF($G39:$G58,"UE",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="37">
+        <f>SUMIF($G39:$G58,"FC",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="37">
+        <f>SUMIF($G39:$G58,"CM",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="37">
+        <f>SUMIF($G39:$G58,"RJ",$H39:$H58)</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="24"/>
+      <c r="I73" s="5"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" s="50">
+        <f t="shared" ref="B74:G74" si="5">100-B73</f>
+        <v>100</v>
+      </c>
+      <c r="C74" s="50">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="D74" s="50">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="E74" s="50">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="F74" s="50">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="G74" s="50">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="H74" s="24"/>
+      <c r="I74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="5"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>